--- a/BWI/bestwine_output/bestwine_Malaysia.xlsx
+++ b/BWI/bestwine_output/bestwine_Malaysia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA165"/>
+  <dimension ref="A1:AA199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17243,6 +17243,2584 @@
       <c r="Z165" s="2" t="inlineStr"/>
       <c r="AA165" s="2" t="inlineStr"/>
     </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HNC Marketing Sdn Bhd </t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Wine Depot Penang</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>168858</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Tanjung Tokong</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Pulau Pinang</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Jalan Fettes</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>11200</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://winedepot.com.my</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>support@winedepot.com.my</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr"/>
+      <c r="P166" s="2" t="inlineStr"/>
+      <c r="Q166" s="2" t="inlineStr"/>
+      <c r="R166" s="2" t="inlineStr"/>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winedepotpenang</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr"/>
+      <c r="X166" s="2" t="inlineStr"/>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Gaia Premium Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr"/>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>168857</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Iskandar Puteri</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Johor</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>B0114, Blok B, Eko Galleria, Jalan Eko Botani 3, Taman Eko Botani</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>79100</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gaiareserve.com</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>gaiau.myofficial@gmail.com</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr"/>
+      <c r="P167" s="2" t="inlineStr"/>
+      <c r="Q167" s="2" t="inlineStr"/>
+      <c r="R167" s="2" t="inlineStr"/>
+      <c r="S167" s="2" t="inlineStr"/>
+      <c r="T167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr"/>
+      <c r="X167" s="2" t="inlineStr"/>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Asia Star Alliance Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr"/>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>168856</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Selangor Darul Ehsan</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Damansara Intan</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>47400</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.asiastaralliance.com</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>enquiry@asiastaralliance.com</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr"/>
+      <c r="P168" s="2" t="inlineStr"/>
+      <c r="Q168" s="2" t="inlineStr"/>
+      <c r="R168" s="2" t="inlineStr"/>
+      <c r="S168" s="2" t="inlineStr"/>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr"/>
+      <c r="X168" s="2" t="inlineStr"/>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>OWB Trading Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Oriental Wines</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>168855</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Sibu</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Sarawak</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>No.15, Drive 1, Brooke Drive</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>96000</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.orientalwines.my</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>orientalwines@yahoo.com</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr"/>
+      <c r="P169" s="2" t="inlineStr"/>
+      <c r="Q169" s="2" t="inlineStr"/>
+      <c r="R169" s="2" t="inlineStr"/>
+      <c r="S169" s="2" t="inlineStr"/>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/owborientalwines_</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr"/>
+      <c r="X169" s="2" t="inlineStr"/>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Rome Century Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>168853</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>No. 31, Tingkat Bawah, Jalan 22/6, Gravitas, Seksyen 22</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>40300</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.romecentury.com</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Romecenturysdnbhd@gmail.com</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr"/>
+      <c r="P170" s="2" t="inlineStr"/>
+      <c r="Q170" s="2" t="inlineStr"/>
+      <c r="R170" s="2" t="inlineStr"/>
+      <c r="S170" s="2" t="inlineStr"/>
+      <c r="T170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>Cheah Wei Ho</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Rome Century Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr"/>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>168853</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>No. 31, Tingkat Bawah, Jalan 22/6, Gravitas, Seksyen 22</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>40300</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.romecentury.com</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Romecenturysdnbhd@gmail.com</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr"/>
+      <c r="P171" s="2" t="inlineStr"/>
+      <c r="Q171" s="2" t="inlineStr"/>
+      <c r="R171" s="2" t="inlineStr"/>
+      <c r="S171" s="2" t="inlineStr"/>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr">
+        <is>
+          <t>Le Thi Tuyet Hanh</t>
+        </is>
+      </c>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Peninsular Imports Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr"/>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>168850</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Lot 107 Jalan Enam, Off Jalan Chan Sow Lin</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>55200</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://peninsular-imports.com</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>info@peninsular-imports.com</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr"/>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr"/>
+      <c r="R172" s="2" t="inlineStr"/>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Peninsularimports/</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>MengHow Tan</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/menghow-tan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pasion Espanola Sdn Bhd </t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Spanish Cellar KL</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>168849</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Federal Territory of Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Jalan Sri Hartamas 17, C-0-3, Puncak Prima Condo</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>50480</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>https://spanishcellarkl.com</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr"/>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>rafiq@pasion-espanola.com</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr"/>
+      <c r="P173" s="2" t="inlineStr"/>
+      <c r="Q173" s="2" t="inlineStr"/>
+      <c r="R173" s="2" t="inlineStr"/>
+      <c r="S173" s="2" t="inlineStr"/>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>Inaz Marissa Dejesus</t>
+        </is>
+      </c>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/inaz-marissa-dejesus-502820252/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armada 1113 Sdn Bhd </t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Armada Market</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>168848</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Kuching</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Sarawak</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>No. 602, Lorong 3, Hui Sing Garden</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>93350</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://armadawine.com</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr"/>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>kuching@armadawine.com</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>+60 82-457 781</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr"/>
+      <c r="Q174" s="2" t="inlineStr"/>
+      <c r="R174" s="2" t="inlineStr"/>
+      <c r="S174" s="2" t="inlineStr"/>
+      <c r="T174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr"/>
+      <c r="X174" s="2" t="inlineStr"/>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Vintage Wines &amp; Spirits Trading Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr"/>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>168847</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Puchong</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Selangor Darul Ehsan</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>100, Jalan Puteri 5/1, Bandar Puteri</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>41700</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vintagewine.com.my</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Vintagews1930@gmail.com</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr"/>
+      <c r="P175" s="2" t="inlineStr"/>
+      <c r="Q175" s="2" t="inlineStr"/>
+      <c r="R175" s="2" t="inlineStr"/>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vintagews</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr"/>
+      <c r="X175" s="2" t="inlineStr"/>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>HOH Wine &amp; Spirit Supplier Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr"/>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>168845</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Johor Bahru</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Johor</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>49 &amp; 51, Jalan Keris 1, Taman Sri Tebrau</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>80050</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hohsupplier.com/contact</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>info@hohwine.my</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr"/>
+      <c r="P176" s="2" t="inlineStr"/>
+      <c r="Q176" s="2" t="inlineStr"/>
+      <c r="R176" s="2" t="inlineStr"/>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hohwineandspirit</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hohwineandspirit/</t>
+        </is>
+      </c>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr"/>
+      <c r="X176" s="2" t="inlineStr"/>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hip Pop Marketing Sdn Bhd </t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>HPM2U</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>168844</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Klang</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>No. 20-G, Jalan Tiara 2A/KU1</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>41150</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>https://hpm2u.com</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>hippopmarketing@gmail.com</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr"/>
+      <c r="P177" s="2" t="inlineStr"/>
+      <c r="Q177" s="2" t="inlineStr"/>
+      <c r="R177" s="2" t="inlineStr"/>
+      <c r="S177" s="2" t="inlineStr"/>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr"/>
+      <c r="W177" s="2" t="inlineStr"/>
+      <c r="X177" s="2" t="inlineStr"/>
+      <c r="Y177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Caldbeck MacGregor Malaysia Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>168841</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Shah Alam</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>No. 9, Jalan Pemaju U1/15, Seksyen U1, Hicom Glenmarie Industrial Park</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>40150</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>https://caldbeckwine.com</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr"/>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>enquiry@caldbecks.com</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-5569 2283</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr"/>
+      <c r="Q178" s="2" t="inlineStr"/>
+      <c r="R178" s="2" t="inlineStr"/>
+      <c r="S178" s="2" t="inlineStr"/>
+      <c r="T178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr"/>
+      <c r="X178" s="2" t="inlineStr"/>
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="AA178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LamboPlace Sdn Bhd </t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>LamboCellar</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>168839</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>8 Persiaran Tropicana, LG Floor, Menara Lien Hoe</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>47410</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lambocellar.com</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr"/>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>hi@lambocellar.com</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7805 7911</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr"/>
+      <c r="Q179" s="2" t="inlineStr"/>
+      <c r="R179" s="2" t="inlineStr"/>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LamboCellar/</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lambocellar/</t>
+        </is>
+      </c>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr"/>
+      <c r="X179" s="2" t="inlineStr"/>
+      <c r="Y179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Legend Worldwide Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr"/>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>168838</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Skudai</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Johor</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>139, Jalan Anggerik Emas 1, Taman Anggerik Emas</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>81200</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.legendworldwide.com.my</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>legendwosb@gmail.com</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr"/>
+      <c r="P180" s="2" t="inlineStr"/>
+      <c r="Q180" s="2" t="inlineStr"/>
+      <c r="R180" s="2" t="inlineStr"/>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/legendworldwidesb/</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr"/>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr"/>
+      <c r="W180" s="2" t="inlineStr"/>
+      <c r="X180" s="2" t="inlineStr"/>
+      <c r="Y180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Loyal Maxim Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr"/>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>168837</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Pulau Langkawi</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Kedah</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Lot 66, No.3, Jalan Pantai Cenang</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>07000</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.loyalmaxim.com.my</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr"/>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>hello@loyalmaxim.com.my</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>+60 4-952 3488</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr"/>
+      <c r="Q181" s="2" t="inlineStr"/>
+      <c r="R181" s="2" t="inlineStr"/>
+      <c r="S181" s="2" t="inlineStr"/>
+      <c r="T181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="inlineStr"/>
+      <c r="W181" s="2" t="inlineStr"/>
+      <c r="X181" s="2" t="inlineStr"/>
+      <c r="Y181" s="2" t="inlineStr"/>
+      <c r="Z181" s="2" t="inlineStr"/>
+      <c r="AA181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Centurion Wines &amp; Spirits Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr"/>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>168836</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Ipoh</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Perak</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>68C, Persiaran Greentown 1, Pusat Perdagangan Greentown</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>30450</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.centurionwines.com</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>centurionwinespirit@gmail.com</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr"/>
+      <c r="P182" s="2" t="inlineStr"/>
+      <c r="Q182" s="2" t="inlineStr"/>
+      <c r="R182" s="2" t="inlineStr"/>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CenturionWinesDirect</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/centurion.wines?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
+        </is>
+      </c>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr"/>
+      <c r="W182" s="2" t="inlineStr"/>
+      <c r="X182" s="2" t="inlineStr"/>
+      <c r="Y182" s="2" t="inlineStr"/>
+      <c r="Z182" s="2" t="inlineStr"/>
+      <c r="AA182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapin International Sdn Bhd </t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr"/>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>168831</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>B-19-07, Menara G-Vestor, Pavilion Embassy, 200, Jalan Ampang</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>50450</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapin.com.my</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr"/>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>info@zapin.com.my</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-3051 5846</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr"/>
+      <c r="Q183" s="2" t="inlineStr"/>
+      <c r="R183" s="2" t="inlineStr"/>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ZapinDutyFree</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/zapindutyfree/</t>
+        </is>
+      </c>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr"/>
+      <c r="W183" s="2" t="inlineStr"/>
+      <c r="X183" s="2" t="inlineStr"/>
+      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Master Suppliers Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr"/>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>168829</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Johor Bahru</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Johor</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>16, Jln Ekoperniagaan 1/17, Taman Ekoperniagaan</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>81100</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mastermssb.com/our-supplies</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr"/>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>ms@mastermssb.com</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>+60 7-288 2278</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr"/>
+      <c r="Q184" s="2" t="inlineStr"/>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/master-suppliers-malaysia</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mastersuppliersmalaysia/</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr"/>
+      <c r="W184" s="2" t="inlineStr">
+        <is>
+          <t>Daryl Sim</t>
+        </is>
+      </c>
+      <c r="X184" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Director</t>
+        </is>
+      </c>
+      <c r="Y184" s="2" t="inlineStr"/>
+      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/daryl-sim-78644256</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Master Suppliers Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr"/>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>168829</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Johor Bahru</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Johor</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>16, Jln Ekoperniagaan 1/17, Taman Ekoperniagaan</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>81100</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mastermssb.com/our-supplies</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr"/>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>ms@mastermssb.com</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>+60 7-288 2278</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr"/>
+      <c r="Q185" s="2" t="inlineStr"/>
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/master-suppliers-malaysia</t>
+        </is>
+      </c>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mastersuppliersmalaysia/</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr">
+        <is>
+          <t>Katherine Choy</t>
+        </is>
+      </c>
+      <c r="X185" s="2" t="inlineStr">
+        <is>
+          <t>Sales Admin Officer</t>
+        </is>
+      </c>
+      <c r="Y185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/katherine-choy-2b890a157</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>House of Hops Distribution</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr"/>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>168828</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>104 Jalan SS 24/2, Taman Megah</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>47301</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>https://houseofhops.com.my</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr"/>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>info@houseofhops.com.my</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr"/>
+      <c r="P186" s="2" t="inlineStr"/>
+      <c r="Q186" s="2" t="inlineStr"/>
+      <c r="R186" s="2" t="inlineStr"/>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/houseofhopsmy</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr">
+        <is>
+          <t>http://instagram.com/houseofhopsmy</t>
+        </is>
+      </c>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr"/>
+      <c r="W186" s="2" t="inlineStr"/>
+      <c r="X186" s="2" t="inlineStr"/>
+      <c r="Y186" s="2" t="inlineStr"/>
+      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>One &amp; Half Liters</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr"/>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>168827</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Sungai Petani</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Kedah</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>No.680E Jalan Kuala Ketil Pekan Lama, Jalan Kuala Ketil Pekan Lama</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>08000</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.onehalfliters.com</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr"/>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>mapleland0224@gmail.com</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr"/>
+      <c r="P187" s="2" t="inlineStr"/>
+      <c r="Q187" s="2" t="inlineStr"/>
+      <c r="R187" s="2" t="inlineStr"/>
+      <c r="S187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100084991726206</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr"/>
+      <c r="X187" s="2" t="inlineStr"/>
+      <c r="Y187" s="2" t="inlineStr"/>
+      <c r="Z187" s="2" t="inlineStr"/>
+      <c r="AA187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Murky Wines &amp; Whisky Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr"/>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>168825</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Gasket Alley</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>https://murkywines.com</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>angel@murkywines.com</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="inlineStr"/>
+      <c r="P188" s="2" t="inlineStr"/>
+      <c r="Q188" s="2" t="inlineStr"/>
+      <c r="R188" s="2" t="inlineStr"/>
+      <c r="S188" s="2" t="inlineStr"/>
+      <c r="T188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/murkywines/</t>
+        </is>
+      </c>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr"/>
+      <c r="W188" s="2" t="inlineStr"/>
+      <c r="X188" s="2" t="inlineStr"/>
+      <c r="Y188" s="2" t="inlineStr"/>
+      <c r="Z188" s="2" t="inlineStr"/>
+      <c r="AA188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Vintteff Trading Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr"/>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>168822</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Federal Territory of Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Scott Garden</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>https://vintteff.com</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr"/>
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>sales@vintteff.com</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr"/>
+      <c r="P189" s="2" t="inlineStr"/>
+      <c r="Q189" s="2" t="inlineStr"/>
+      <c r="R189" s="2" t="inlineStr"/>
+      <c r="S189" s="2" t="inlineStr"/>
+      <c r="T189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vintteff/</t>
+        </is>
+      </c>
+      <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="2" t="inlineStr"/>
+      <c r="W189" s="2" t="inlineStr"/>
+      <c r="X189" s="2" t="inlineStr"/>
+      <c r="Y189" s="2" t="inlineStr"/>
+      <c r="Z189" s="2" t="inlineStr"/>
+      <c r="AA189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>DC Selections Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr"/>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>168821</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>No 28, Jalan Metro Pudu 2, Fraser Business Park</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>55100</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>https://dcselections.com.my</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr"/>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>admin@dcselections.com.my</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="inlineStr"/>
+      <c r="P190" s="2" t="inlineStr"/>
+      <c r="Q190" s="2" t="inlineStr"/>
+      <c r="R190" s="2" t="inlineStr"/>
+      <c r="S190" s="2" t="inlineStr"/>
+      <c r="T190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dcselections/</t>
+        </is>
+      </c>
+      <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="2" t="inlineStr"/>
+      <c r="W190" s="2" t="inlineStr"/>
+      <c r="X190" s="2" t="inlineStr"/>
+      <c r="Y190" s="2" t="inlineStr"/>
+      <c r="Z190" s="2" t="inlineStr"/>
+      <c r="AA190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Chop Kim Hong</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr"/>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>168819</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Kulai</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Johor</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>TS 14, Jalan Lengkongan</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>81000</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>https://chopkimhong.com</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr"/>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>contact@chopkimhong.com</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>+60 7-663 1573</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr"/>
+      <c r="Q191" s="2" t="inlineStr"/>
+      <c r="R191" s="2" t="inlineStr"/>
+      <c r="S191" s="2" t="inlineStr"/>
+      <c r="T191" s="2" t="inlineStr"/>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr"/>
+      <c r="W191" s="2" t="inlineStr"/>
+      <c r="X191" s="2" t="inlineStr"/>
+      <c r="Y191" s="2" t="inlineStr"/>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Bordeaux Cellar 1855 Vin (M) Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr"/>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>168818</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>6, Jln 51/203A, Pjs 51</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>46050</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>https://bordeauxcellar1855.com.my</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr"/>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>bordeaux1855@yahoo.com</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr"/>
+      <c r="P192" s="2" t="inlineStr"/>
+      <c r="Q192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr"/>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bordeauxcellar/</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bordeauxcellar1855hq/</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr"/>
+      <c r="W192" s="2" t="inlineStr"/>
+      <c r="X192" s="2" t="inlineStr"/>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Mirage Synergy Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr"/>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>168817</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Seri Kembangan</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Selangor Darul Ehsan</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>No. 35, Jalan BS 7/1D, Seksyen 7, Taman Perindustrian Bukit Serdang</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>43300</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miragesynergy.com</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr"/>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>info@miragesynergy.com</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-8942 1388</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr"/>
+      <c r="Q193" s="2" t="inlineStr"/>
+      <c r="R193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/miragesynergy</t>
+        </is>
+      </c>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/miragesynergy/</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mirage.synergy/</t>
+        </is>
+      </c>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="W193" s="2" t="inlineStr">
+        <is>
+          <t>August Tee</t>
+        </is>
+      </c>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/august-tee-799370180/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Mirage Synergy Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr"/>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>168817</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Seri Kembangan</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Selangor Darul Ehsan</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>No. 35, Jalan BS 7/1D, Seksyen 7, Taman Perindustrian Bukit Serdang</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>43300</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miragesynergy.com</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr"/>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>info@miragesynergy.com</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-8942 1388</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr"/>
+      <c r="Q194" s="2" t="inlineStr"/>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/miragesynergy</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/miragesynergy/</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mirage.synergy/</t>
+        </is>
+      </c>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr">
+        <is>
+          <t>Yumiko Yap</t>
+        </is>
+      </c>
+      <c r="X194" s="2" t="inlineStr">
+        <is>
+          <t>Logistics &amp; Account Executive</t>
+        </is>
+      </c>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/yumiko-yap-a72574267</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Mirage Synergy Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr"/>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>168817</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Seri Kembangan</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Selangor Darul Ehsan</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>No. 35, Jalan BS 7/1D, Seksyen 7, Taman Perindustrian Bukit Serdang</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>43300</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miragesynergy.com</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr"/>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>info@miragesynergy.com</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-8942 1388</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr"/>
+      <c r="Q195" s="2" t="inlineStr"/>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/miragesynergy</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/miragesynergy/</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mirage.synergy/</t>
+        </is>
+      </c>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr"/>
+      <c r="W195" s="2" t="inlineStr">
+        <is>
+          <t>Carson Cl</t>
+        </is>
+      </c>
+      <c r="X195" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr"/>
+      <c r="AA195" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/carson-cl-2620202bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Sin Li Wines &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr"/>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>168816</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Skudai</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Johor</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>No.22,22A, Jalan Nakhoda 12, Taman Ungku Tun Aminah</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>81300</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>https://sinliwines.online/our-business</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr"/>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>sinliwines13@gmail.com</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr"/>
+      <c r="P196" s="2" t="inlineStr"/>
+      <c r="Q196" s="2" t="inlineStr"/>
+      <c r="R196" s="2" t="inlineStr"/>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sinliwinesshop/</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sinliwines/</t>
+        </is>
+      </c>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="2" t="inlineStr"/>
+      <c r="W196" s="2" t="inlineStr"/>
+      <c r="X196" s="2" t="inlineStr"/>
+      <c r="Y196" s="2" t="inlineStr"/>
+      <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>The Vintage Wine Club Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>The Vintage Wine Club</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>168815</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Unit A1-G1-3, Solaris Dutamas, No 1 Jalan Dutamas</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>50480</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thevintageclub.my</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr"/>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>admin@thevintageclub.my</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr"/>
+      <c r="P197" s="2" t="inlineStr"/>
+      <c r="Q197" s="2" t="inlineStr"/>
+      <c r="R197" s="2" t="inlineStr"/>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61574381183558</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thevintagewineclub_my/</t>
+        </is>
+      </c>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr"/>
+      <c r="W197" s="2" t="inlineStr"/>
+      <c r="X197" s="2" t="inlineStr"/>
+      <c r="Y197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Cave &amp; Cellar Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr"/>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>168814</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Petaling Jaya</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>47 Jalan PJU 1A/16 Ara Damansara</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>46050</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>https://caveandcellarmy.wordpress.com</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr"/>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>marketing@cavcel.com.my</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>+60 3-7845 0670</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr"/>
+      <c r="Q198" s="2" t="inlineStr"/>
+      <c r="R198" s="2" t="inlineStr"/>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavecellar</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cave_cellar/</t>
+        </is>
+      </c>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr"/>
+      <c r="W198" s="2" t="inlineStr">
+        <is>
+          <t>Candy Mah</t>
+        </is>
+      </c>
+      <c r="X198" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="Y198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/candy-mah-2abb3053/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Dionysus Asia Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Dionysus Asia Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>24470</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>16 Jalan Metro Perdana Barat 12</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>52100</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>https://crackabottle.com</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>crackabottlemalaysia@gmail.com</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr"/>
+      <c r="P199" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>201001027841</t>
+        </is>
+      </c>
+      <c r="R199" s="2" t="inlineStr"/>
+      <c r="S199" s="2" t="inlineStr"/>
+      <c r="T199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dionysus.asia/</t>
+        </is>
+      </c>
+      <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@crackabottle4886</t>
+        </is>
+      </c>
+      <c r="W199" s="2" t="inlineStr"/>
+      <c r="X199" s="2" t="inlineStr"/>
+      <c r="Y199" s="2" t="inlineStr"/>
+      <c r="Z199" s="2" t="inlineStr"/>
+      <c r="AA199" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Malaysia.xlsx
+++ b/BWI/bestwine_output/bestwine_Malaysia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA199"/>
+  <dimension ref="A1:AA200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19821,6 +19821,95 @@
       <c r="Z199" s="2" t="inlineStr"/>
       <c r="AA199" s="2" t="inlineStr"/>
     </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Dionysus Asia Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Dionysus Asia Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>24470</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>16 Jalan Metro Perdana Barat 12</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>52100</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>https://crackabottle.com</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>crackabottlemalaysia@gmail.com</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr"/>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>201001027841</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="inlineStr"/>
+      <c r="S200" s="2" t="inlineStr"/>
+      <c r="T200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dionysus.asia/</t>
+        </is>
+      </c>
+      <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@crackabottle4886</t>
+        </is>
+      </c>
+      <c r="W200" s="2" t="inlineStr"/>
+      <c r="X200" s="2" t="inlineStr"/>
+      <c r="Y200" s="2" t="inlineStr"/>
+      <c r="Z200" s="2" t="inlineStr"/>
+      <c r="AA200" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
